--- a/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado</t>
+          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,36</t>
+          <t>7,09; 10,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,48</t>
+          <t>7,11; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,85</t>
+          <t>6,53; 10,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 9,97</t>
+          <t>6,7; 9,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,36</t>
+          <t>7,17; 9,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,36</t>
+          <t>6,35; 10,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,38</t>
+          <t>7,1; 9,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,95</t>
+          <t>7,42; 8,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 9,51</t>
+          <t>6,9; 9,59</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,69</t>
+          <t>6,73; 7,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,95</t>
+          <t>7,0; 7,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,54</t>
+          <t>7,45; 8,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,59</t>
+          <t>6,67; 7,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,46</t>
+          <t>7,32; 8,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,13</t>
+          <t>6,58; 8,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,51</t>
+          <t>6,82; 7,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 8,02</t>
+          <t>7,32; 8,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,05</t>
+          <t>7,17; 8,09</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 7,76</t>
+          <t>6,17; 7,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,23</t>
+          <t>7,3; 11,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 9,63</t>
+          <t>7,6; 9,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 7,82</t>
+          <t>6,75; 7,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,26</t>
+          <t>7,1; 8,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,95</t>
+          <t>6,93; 7,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,56</t>
+          <t>6,62; 7,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,36</t>
+          <t>7,43; 9,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,38</t>
+          <t>7,33; 8,42</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,64</t>
+          <t>6,82; 7,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,57</t>
+          <t>7,39; 8,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 8,62</t>
+          <t>7,68; 8,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,65</t>
+          <t>6,9; 7,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,21</t>
+          <t>7,46; 8,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,91</t>
+          <t>6,82; 7,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,52</t>
+          <t>6,95; 7,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,21</t>
+          <t>7,51; 8,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,03</t>
+          <t>7,38; 8,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,23</t>
+          <t>7,07; 10,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,4</t>
+          <t>7,22; 9,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,69</t>
+          <t>6,7; 9,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,33</t>
+          <t>7,25; 9,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,33</t>
+          <t>6,38; 10,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,22</t>
+          <t>7,04; 9,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,93</t>
+          <t>7,33; 8,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 9,59</t>
+          <t>6,82; 9,68</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 7,72</t>
+          <t>6,73; 7,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,89</t>
+          <t>7,05; 7,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,54</t>
+          <t>7,46; 8,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,61</t>
+          <t>6,67; 7,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,41</t>
+          <t>7,32; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,09</t>
+          <t>6,59; 8,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,47</t>
+          <t>6,82; 7,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,05</t>
+          <t>7,31; 8,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,09</t>
+          <t>7,17; 8,04</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,8</t>
+          <t>6,08; 7,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,78</t>
+          <t>7,36; 12,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 9,45</t>
+          <t>7,6; 9,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,86</t>
+          <t>6,75; 7,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,26</t>
+          <t>7,13; 8,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,97</t>
+          <t>6,89; 7,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,59</t>
+          <t>6,6; 7,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,41</t>
+          <t>7,47; 9,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,42</t>
+          <t>7,35; 8,41</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,65</t>
+          <t>6,79; 7,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,51</t>
+          <t>7,42; 8,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,6</t>
+          <t>7,68; 8,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,23</t>
+          <t>7,38; 8,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,87</t>
+          <t>6,82; 7,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,51</t>
+          <t>6,94; 7,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,21</t>
+          <t>7,53; 8,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,06</t>
+          <t>7,34; 8,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,67</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,92</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,14</t>
+          <t>6,69; 9,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,49</t>
+          <t>7,17; 9,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,59</t>
+          <t>6,37; 10,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,82</t>
+          <t>7,02; 10,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,19</t>
+          <t>7,12; 9,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,96</t>
+          <t>6,71; 10,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 9,47</t>
+          <t>7,18; 9,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,94</t>
+          <t>7,38; 8,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,68</t>
+          <t>6,85; 9,51</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,82</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>7,15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,47</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,95</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,12</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 7,73</t>
+          <t>6,69; 7,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,91</t>
+          <t>7,31; 8,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>6,55; 8,13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6,75; 7,69</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,06; 7,95</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>7,46; 8,54</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6,67; 7,63</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,32; 8,39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,59; 8,2</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,49</t>
+          <t>6,83; 7,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,02</t>
+          <t>7,34; 8,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,04</t>
+          <t>7,17; 8,05</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,68</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,46</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,39</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,68</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 7,74</t>
+          <t>6,73; 7,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,12</t>
+          <t>7,14; 8,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 9,48</t>
+          <t>6,87; 7,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,77</t>
+          <t>6,04; 7,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,28</t>
+          <t>7,33; 11,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,93</t>
+          <t>7,59; 9,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,58</t>
+          <t>6,62; 7,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,46</t>
+          <t>7,47; 9,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,41</t>
+          <t>7,33; 8,38</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,79</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,79</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,09</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,22</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,65</t>
+          <t>6,89; 7,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,57</t>
+          <t>7,42; 8,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,59</t>
+          <t>6,85; 7,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,64</t>
+          <t>6,8; 7,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,17</t>
+          <t>7,37; 8,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,88</t>
+          <t>7,69; 8,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,49</t>
+          <t>6,98; 7,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,22</t>
+          <t>7,52; 8,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 8,04</t>
+          <t>7,37; 8,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,67</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,31</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,98</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,08</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8,0</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.807865292966293</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7.918692512196437</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.667085604501675</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>8.232403807910286</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>8.192324179061913</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>8.310848096512265</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>7.984006938564136</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>8.077288703421464</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>8.00134283286258</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6,69; 9,97</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,17; 9,36</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,37; 10,36</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7,02; 10,36</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,12; 9,48</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,71; 10,85</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,18; 9,38</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,38; 8,95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 9,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>6.689577353630722</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7.167179774316477</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.369442483154691</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>7.021467003480041</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>7.120777021824169</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>6.70536528830096</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>7.1803467238929</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.379292838137284</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>6.850490431395287</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.970270073818558</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.355516727016139</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.36226075331094</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.35579393256124</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.482742637028499</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.85235782536127</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9.381408636828455</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>8.94818013519876</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>9.510815929211555</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7,12</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,47</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,14</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,69; 7,59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,31; 8,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,55; 8,13</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6,75; 7,69</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,06; 7,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,46; 8,54</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,83; 7,51</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,34; 8,02</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7,17; 8,05</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>7.122505156149586</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.816236725489669</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.149737522171889</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7.154673435534802</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7.465576835613584</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>7.945759116585897</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>7.137724670269939</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>7.643658944488819</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7.565809148015537</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,68</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,46</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,39</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,09</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8,03</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7,81</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6.687551743100141</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7.313098098646398</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6.548814260087985</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>6.747295408285032</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7.063601751630863</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>7.455138625031367</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>6.828565836188378</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>7.34209024809879</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>7.169570120735507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,73; 7,82</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 8,26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,87; 7,95</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6,04; 7,76</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,33; 11,23</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,59; 9,63</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,62; 7,56</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7,47; 9,36</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>7,33; 8,38</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.589058638115124</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.461671396324343</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.129244572217614</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.693616659390818</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>7.951958623852209</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>8.541298343243229</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>7.50534461575449</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>8.015109617276854</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>8.0480414061737</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,22</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,21</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>7.190130842986864</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.681935952818835</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.347946026257979</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.980272140432853</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8.45564738673183</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>8.388970882010428</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>7.090090606765852</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>8.030327374897237</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>7.814256577155895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>6,89; 7,65</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 8,21</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,91</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 7,64</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,57</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,69; 8,62</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,98; 7,52</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 8,21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.727130594887206</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>7.143568276588749</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>6.866536319566213</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>6.04208458182167</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>7.331909324350519</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>7.593497106644391</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>6.622841826675691</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>7.467993867117328</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7.326304381675737</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.816971980844237</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.26275266100687</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.949341839941121</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.761174678154122</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>11.23478607907272</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>9.634840482514782</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7.559902088550101</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.360795515423437</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8.380372220462865</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.223936023680416</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.78669216585527</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7.241462922260872</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7.201851859521645</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7.793434878057755</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>8.090397653694831</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7.213600715818909</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>7.789996458275741</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7.664646716399024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6.891294806555661</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7.421563673088825</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>6.853564913398673</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>6.797748991603733</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.373357305316943</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>7.690486094829057</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>6.983596481502146</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>7.522212523575002</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7.366378571170508</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.646638322078542</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.209710042480397</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.907356058578277</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.639725248553726</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8.571050751942703</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>8.616580532381422</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>7.517069346887558</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>8.213203967999696</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>8.032875538653988</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
